--- a/fem-artifacts/main_artifacts_updated.xlsx
+++ b/fem-artifacts/main_artifacts_updated.xlsx
@@ -23927,7 +23927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z148"/>
+  <dimension ref="A1:Z202"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.42578125" defaultRowHeight="15"/>
   <cols>
     <col width="7.7109375" customWidth="1" style="74" min="1" max="1"/>
@@ -27829,12 +27829,12 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Билеты (ж.д. сообщение, плацкарт, 2 направления)</t>
+          <t>Менеджер проектов</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -27844,22 +27844,22 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Билеты (ж.д. сообщение, купе, 2 направления)</t>
+          <t>Технический директор</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -27869,22 +27869,22 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Билеты (авиа сообщение,  2 направления)</t>
+          <t>Инженер контроля качества</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -27894,22 +27894,22 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Проживание (сутки гостиница для производств.сотрудников)</t>
+          <t>Бухгалтер</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -27919,22 +27919,22 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Проживание (сутки гостиница для АУП)</t>
+          <t>Директор филиала</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -27944,22 +27944,22 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Суточные (6 мрп)</t>
+          <t>Юрист</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -27969,7 +27969,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
         </is>
       </c>
       <c r="M93" t="n">
@@ -27979,12 +27979,12 @@
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>7. Расчет экспл.расх</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ДТ для ДГУ</t>
+          <t>Инспектор по кадрам</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -27994,11 +27994,11 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
@@ -28009,7 +28009,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Охрана</t>
+          <t>Билеты (ж.д. сообщение, плацкарт, 2 направления)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
@@ -28034,7 +28034,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Канц. Товары</t>
+          <t>Билеты (ж.д. сообщение, купе, 2 направления)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -28048,7 +28048,7 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -28059,7 +28059,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Хоз. Товары</t>
+          <t>Билеты (авиа сообщение,  2 направления)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -28073,7 +28073,7 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Клининговые услуги</t>
+          <t>Проживание (сутки гостиница для производств.сотрудников)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -28098,7 +28098,7 @@
         </is>
       </c>
       <c r="M98" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -28109,7 +28109,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ГСМ для сотрудников</t>
+          <t>Проживание (сутки гостиница для АУП)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -28119,197 +28119,197 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Туркестан фин 04.11.2025.xlsx::5. Экспл; ФЭМ №1 (Павлодар).xlsx::5. Экспл</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>Оснащение рабочих мест Ситуационного центра</t>
+          <t>Экономические предположения</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Оснащение оборудованием ситуационного центра</t>
+          <t>Суточные (6 мрп)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>4. Шу_ФЭМ.xlsx::3. Инвест; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ №1 (Павлодар).xlsx::3. Инвест; ФЭМ №2 (Павлодар).xlsx::3. Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t>Инвест</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Метеостанция: PM 2.5, PM10, ветер, температура, осадки</t>
+          <t>Водитель логист</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест; ФЭМ_Атырау.xlsx::Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ; ФЭМ_проекта_Жетысу_final.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>Инвест</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Планшет, принтер, ПО</t>
+          <t>Офис-менеджер</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест; ФЭМ_Атырау.xlsx::Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ; ФЭМ_проекта_Жетысу_final.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
+          <t>7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Затраты на оборудование для интеграции на 1 существующую камеру</t>
+          <t>ДТ для ДГУ</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест; ФЭМ_Атырау.xlsx::Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M103" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Экономические предположения</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>АПК "Сергек.Линейный"</t>
+          <t>Охрана</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Экономические предположения</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>АПК "Сергек.Перекресток"</t>
+          <t>Канц. Товары</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M105" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
+          <t>Экономические предположения</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>монтаж оборудования для интеграции</t>
+          <t>Хоз. Товары</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест; ФЭМ_Атырау.xlsx::Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M106" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t>7. Расчет экспл.расх</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Канал передачи данных - центральный узел</t>
+          <t>Экономист</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -28319,97 +28319,97 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх; ФЭМ №1 (Павлодар).xlsx::5. Экспл; ФЭМ_Туркестан_1006.xlsx::Экспл</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M107" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" t="inlineStr">
         <is>
-          <t>Оснащение рабочих мест Ситуационного центра</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Мобильное рабочее место + лицензия MDM</t>
+          <t>Менеджер отдела закупа</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>4. Шу_ФЭМ.xlsx::3. Инвест; ФЭМ_проекта_Жетысу_final.xlsx::3. Инвест; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::3. Инвест; ФЭМ_проекта_Курмангазы v.8.xlsx::3. Инвест</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M108" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t>Центр обработки и анализа данных</t>
+          <t>Экономические предположения</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Система серверов процессинга и аналитики, включая ПО</t>
+          <t>Клининговые услуги</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M109" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="inlineStr">
         <is>
-          <t>Центр обработки и анализа данных</t>
+          <t>Экономические предположения</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Система серверов хранения данных, включая ПО</t>
+          <t>ГСМ для сотрудников</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест</t>
+          <t>4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Туркестан фин 04.11.2025.xlsx::5. Экспл; ФЭМ №1 (Павлодар).xlsx::5. Экспл</t>
         </is>
       </c>
       <c r="M110" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" t="inlineStr">
         <is>
-          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
+          <t>Оснащение рабочих мест Ситуационного центра</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>монтаж оборудования линейных участков</t>
+          <t>Оснащение оборудованием ситуационного центра</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -28419,47 +28419,47 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест</t>
+          <t>4. Шу_ФЭМ.xlsx::3. Инвест; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ №1 (Павлодар).xlsx::3. Инвест; ФЭМ №2 (Павлодар).xlsx::3. Инвест</t>
         </is>
       </c>
       <c r="M111" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="inlineStr">
         <is>
-          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>монтаж оборудования перекрестков</t>
+          <t>Старший инженер контроля качества</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ_проекта_Жетысу_final.xlsx::6. ФОТ; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M112" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="inlineStr">
         <is>
-          <t>4.CAPEX</t>
+          <t>Инвест</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Инструменты и средства индивидуальной защиты</t>
+          <t>Метеостанция: PM 2.5, PM10, ветер, температура, осадки</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -28469,22 +28469,22 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ №1 (Павлодар).xlsx::3. Инвест; ФЭМ №2 (Павлодар).xlsx::3. Инвест</t>
+          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест; ФЭМ_Атырау.xlsx::Инвест</t>
         </is>
       </c>
       <c r="M113" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Инвест</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Аппаратно-программный комплекс на линейном участке</t>
+          <t>Планшет, принтер, ПО</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -28494,22 +28494,22 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ_ДС_09_06_2025_для_нового_состава_2 (2).xlsx::3. Инвест</t>
+          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест; ФЭМ_Атырау.xlsx::Инвест</t>
         </is>
       </c>
       <c r="M114" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Аппаратно-программный комплекс на перекрестке</t>
+          <t>Затраты на оборудование для интеграции на 1 существующую камеру</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -28519,11 +28519,11 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ_ДС_09_06_2025_для_нового_состава_2 (2).xlsx::3. Инвест</t>
+          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест; ФЭМ_Атырау.xlsx::Инвест</t>
         </is>
       </c>
       <c r="M115" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Мобильное рабочее место</t>
+          <t>АПК "Сергек.Линейный"</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -28544,22 +28544,22 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ_ДС_09_06_2025_для_нового_состава_2 (2).xlsx::3. Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t>Инструменты и средства индивидуальной защиты</t>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Мобильный интеллектуальный АПК</t>
+          <t>АПК "Сергек.Перекресток"</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -28569,22 +28569,22 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ_ДС_09_06_2025_для_нового_состава_2 (2).xlsx::3. Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M117" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t>Инструменты и средства индивидуальной защиты</t>
+          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Транспортный двойник города</t>
+          <t>монтаж оборудования для интеграции</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -28594,22 +28594,22 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ_ДС_09_06_2025_для_нового_состава_2 (2).xlsx::3. Инвест</t>
+          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест; ФЭМ_Атырау.xlsx::Инвест</t>
         </is>
       </c>
       <c r="M118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" t="inlineStr">
         <is>
-          <t>Экспл</t>
+          <t>7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Аренда ЦОД</t>
+          <t>Канал передачи данных - центральный узел</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -28619,36 +28619,36 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>ФЭМ ИТОГ до ноября24.xlsx::Экспл; ФЭМ_Астана (4).xlsx::Экспл</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх; ФЭМ №1 (Павлодар).xlsx::5. Экспл; ФЭМ_Туркестан_1006.xlsx::Экспл</t>
         </is>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t>Экспл</t>
+          <t>Оснащение рабочих мест Ситуационного центра</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Коммунальные расходы (электроэнергия)</t>
+          <t>Мобильное рабочее место + лицензия MDM</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>ФЭМ ИТОГ до ноября24.xlsx::Экспл; ФЭМ_Астана (4).xlsx::Экспл</t>
+          <t>4. Шу_ФЭМ.xlsx::3. Инвест; ФЭМ_проекта_Жетысу_final.xlsx::3. Инвест; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::3. Инвест; ФЭМ_проекта_Курмангазы v.8.xlsx::3. Инвест</t>
         </is>
       </c>
       <c r="M120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Сервера хранения данных, 1 ПТб</t>
+          <t>Система серверов процессинга и аналитики, включая ПО</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -28669,22 +28669,22 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>ФЭМ_Атырау.xlsx::Инвест</t>
+          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест</t>
         </is>
       </c>
       <c r="M121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t>Инвест</t>
+          <t>Центр обработки и анализа данных</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Расходные материалы на подключение к сети</t>
+          <t>Система серверов хранения данных, включая ПО</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -28694,22 +28694,22 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>ФЭМ_Атырау.xlsx::Инвест</t>
+          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест</t>
         </is>
       </c>
       <c r="M122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
       <c r="B123" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Аппаратно-программный комплек "Сергек. Патруль BOX"</t>
+          <t>монтаж оборудования линейных участков</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -28719,11 +28719,11 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>ФЭМ_проекта_Жетысу_final.xlsx::3. Инвест; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::3. Инвест; ФЭМ_проекта_Курмангазы v.8.xlsx::3. Инвест</t>
+          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест</t>
         </is>
       </c>
       <c r="M123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Монтаж АПК патруль</t>
+          <t>монтаж оборудования перекрестков</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -28744,22 +28744,22 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>ФЭМ_проекта_Жетысу_final.xlsx::3. Инвест; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::3. Инвест; ФЭМ_проекта_Курмангазы v.8.xlsx::3. Инвест</t>
+          <t>ФЭМ ИСХОДНАЯ.xlsx::Инвест; ФЭМ ИТОГ до ноября24.xlsx::Инвест; ФЭМ_16_07_приложение_к_доп_согл.xlsx::Инвест; ФЭМ_Астана (4).xlsx::Инвест</t>
         </is>
       </c>
       <c r="M124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t>5. Экспл</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Обслуживание  АПК "Патруль"</t>
+          <t>Ведущий инженер контроля качества</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -28769,36 +28769,36 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>ФЭМ_проекта_Жетысу_final.xlsx::5. Экспл; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::5. Экспл; ФЭМ_проекта_Курмангазы v.8.xlsx::5. Экспл</t>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
         </is>
       </c>
       <c r="M125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Счетчики АСКУЭ для АПК "Сергек"</t>
+          <t>Инженер сетей</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
+          <t>ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ; финал_ФЭМ_проекта_Туркестан_расширение_и_продление_v_2_с_помесячн_графиком.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
@@ -28809,7 +28809,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Универсальный шлюз безопасности (NGFW)</t>
+          <t>Инструменты и средства индивидуальной защиты</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -28819,22 +28819,22 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ №1 (Павлодар).xlsx::3. Инвест; ФЭМ №2 (Павлодар).xlsx::3. Инвест</t>
         </is>
       </c>
       <c r="M127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" t="inlineStr">
         <is>
-          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Монтаж АПК "Сергек.Линейный"</t>
+          <t>Аппаратно-программный комплекс на линейном участке</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -28844,22 +28844,22 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
+          <t>Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ_ДС_09_06_2025_для_нового_состава_2 (2).xlsx::3. Инвест</t>
         </is>
       </c>
       <c r="M128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
-          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Монтаж АПК "Сергек.Перекресток"</t>
+          <t>Аппаратно-программный комплекс на перекрестке</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -28869,11 +28869,11 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
+          <t>Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ_ДС_09_06_2025_для_нового_состава_2 (2).xlsx::3. Инвест</t>
         </is>
       </c>
       <c r="M129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Подключение каналов связи (АПК "Сергек")</t>
+          <t>Мобильное рабочее место</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -28894,22 +28894,22 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
+          <t>Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ_ДС_09_06_2025_для_нового_состава_2 (2).xlsx::3. Инвест</t>
         </is>
       </c>
       <c r="M130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Инструменты и средства индивидуальной защиты</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Поверка (АПК "Сергек")</t>
+          <t>Мобильный интеллектуальный АПК</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -28919,22 +28919,22 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
+          <t>Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ_ДС_09_06_2025_для_нового_состава_2 (2).xlsx::3. Инвест</t>
         </is>
       </c>
       <c r="M131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" t="inlineStr">
         <is>
-          <t>Для CAPEX</t>
+          <t>Инструменты и средства индивидуальной защиты</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Зарядное устройство С 4/36-90 230V box</t>
+          <t>Транспортный двойник города</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -28944,22 +28944,22 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::Для CAPEX; ФЭМ Костанай.xlsx::Для CAPEX</t>
+          <t>Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::3. Инвест; ФЭМ ДС №2 Алмобл 26.02 .xlsx::3. Инвест; ФЭМ_ДС_09_06_2025_для_нового_состава_2 (2).xlsx::3. Инвест</t>
         </is>
       </c>
       <c r="M132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Экспл</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Канал передачи данных - АПК "Сергек.Линейный"</t>
+          <t>Аренда ЦОД</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -28969,22 +28969,22 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::Экспл; ФЭМ_Астана (4).xlsx::Экспл</t>
         </is>
       </c>
       <c r="M133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Экспл</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Канал передачи данных - АПК "Сергек.Перекресток"</t>
+          <t>Коммунальные расходы (электроэнергия)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -28994,47 +28994,47 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::Экспл; ФЭМ_Астана (4).xlsx::Экспл</t>
         </is>
       </c>
       <c r="M134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" t="inlineStr">
         <is>
-          <t>Центр обработки и анализа данных</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Резервный сервер</t>
+          <t>Ведущий менеджер проектов</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>4. Шу_ФЭМ.xlsx::3. Инвест; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::3. Инвест</t>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
         </is>
       </c>
       <c r="M135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Центр обработки и анализа данных</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Мобильное рабочее место "Сергек"</t>
+          <t>Сервера хранения данных, 1 ПТб</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -29044,47 +29044,47 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>ФЭМ №1 (Павлодар).xlsx::3. Инвест; ФЭМ №2 (Павлодар).xlsx::3. Инвест</t>
+          <t>ФЭМ_Атырау.xlsx::Инвест</t>
         </is>
       </c>
       <c r="M136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Инвест</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Распределение расходов административно-управленческого персонала,осуществляющего поддержку проекта Астана - Сергек ( прочие расходы)</t>
+          <t>Расходные материалы на подключение к сети</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>ФЭМ_Астана (4).xlsx::Обсл; ФЭМ_Астана (4).xlsx::Экспл</t>
+          <t>ФЭМ_Атырау.xlsx::Инвест</t>
         </is>
       </c>
       <c r="M137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t>Инвест</t>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Видеостена под ключ</t>
+          <t>Аппаратно-программный комплек "Сергек. Патруль BOX"</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -29094,22 +29094,22 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>ФЭМ_Атырау.xlsx::Инвест</t>
+          <t>ФЭМ_проекта_Жетысу_final.xlsx::3. Инвест; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::3. Инвест; ФЭМ_проекта_Курмангазы v.8.xlsx::3. Инвест</t>
         </is>
       </c>
       <c r="M138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Аппаратно-программный комплекс "Сергек. Трасса" v4.0</t>
+          <t>Монтаж АПК патруль</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -29119,36 +29119,36 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::3. Инвест; ФЭМ_проекта_Курмангазы v.8.xlsx::3. Инвест</t>
+          <t>ФЭМ_проекта_Жетысу_final.xlsx::3. Инвест; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::3. Инвест; ФЭМ_проекта_Курмангазы v.8.xlsx::3. Инвест</t>
         </is>
       </c>
       <c r="M139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" t="inlineStr">
         <is>
-          <t>4.CAPEX</t>
+          <t>5. Экспл</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Видеостена (13500х6500), под ключ</t>
+          <t>Обслуживание  АПК "Патруль"</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX</t>
+          <t>ФЭМ_проекта_Жетысу_final.xlsx::5. Экспл; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::5. Экспл; ФЭМ_проекта_Курмангазы v.8.xlsx::5. Экспл</t>
         </is>
       </c>
       <c r="M140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -29159,7 +29159,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Аппаратно-программный комплекс "Сергек. Патруль"</t>
+          <t>Счетчики АСКУЭ для АПК "Сергек"</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -29169,22 +29169,22 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>4. Шу_ФЭМ.xlsx::3. Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
         </is>
       </c>
       <c r="M141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>4.CAPEX</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Аппаратно-программный комплекс "Сергек. Трасса"</t>
+          <t>Универсальный шлюз безопасности (NGFW)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -29194,47 +29194,47 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>4. Шу_ФЭМ.xlsx::3. Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
         </is>
       </c>
       <c r="M142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Распределение расходов административно-управленческого персонала,осуществляющего поддержку проекта Астана - Сергек за  декабрь 2022г. ( прочие расходы)</t>
+          <t>Монтаж АПК "Сергек.Линейный"</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>ФЭМ ИТОГ до ноября24.xlsx::Обсл</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
         </is>
       </c>
       <c r="M143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Стоимость монтажных работ и услуг для запуска проекта</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>АПК "Сергек" на линейных участках</t>
+          <t>Монтаж АПК "Сергек.Перекресток"</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -29244,11 +29244,11 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>ФЭМ Костанай.xlsx::4.CAPEX</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
         </is>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -29259,7 +29259,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>АПК "Сергек" на перекрестках</t>
+          <t>Подключение каналов связи (АПК "Сергек")</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -29269,11 +29269,11 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>ФЭМ Костанай.xlsx::4.CAPEX</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
         </is>
       </c>
       <c r="M145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -29284,7 +29284,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Аппаратно-программный комплекс "Сергек. Трассы"</t>
+          <t>Поверка (АПК "Сергек")</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29294,22 +29294,22 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>ФЭМ №2 (Павлодар).xlsx::3. Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX; ФЭМ Костанай.xlsx::4.CAPEX</t>
         </is>
       </c>
       <c r="M146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Для CAPEX</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Аппаратно-программный комплекс "Сергек. Линейный участок" v4.0 на трассах</t>
+          <t>Зарядное устройство С 4/36-90 230V box</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29319,35 +29319,1385 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>ФЭМ_проекта_Жетысу_final.xlsx::3. Инвест</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::Для CAPEX; ФЭМ Костанай.xlsx::Для CAPEX</t>
         </is>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" t="inlineStr">
         <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Старший специалист по тех. поддержке</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
+        </is>
+      </c>
+      <c r="M148" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Специалист по тех. поддержке</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
+        </is>
+      </c>
+      <c r="M149" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Менеджер по технике безопасности</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Калибровщик</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Логист тестировщик</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
+        </is>
+      </c>
+      <c r="M152" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
           <t>Аппаратно-программные комплексы "Сергек"</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Канал передачи данных - АПК "Сергек.Линейный"</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+        </is>
+      </c>
+      <c r="M153" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Канал передачи данных - АПК "Сергек.Перекресток"</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+        </is>
+      </c>
+      <c r="M154" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Центр обработки и анализа данных</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Резервный сервер</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>4. Шу_ФЭМ.xlsx::3. Инвест; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::3. Инвест</t>
+        </is>
+      </c>
+      <c r="M155" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Заместитель директора филиала</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M156" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Менеджер мониторинга</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M157" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ассистент руководителя</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M158" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Главный инженер контроля качества</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M159" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Ведущий инженер по сервисам</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M160" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Инженер по сервисам</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M161" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Логист</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M162" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Генеральный директор</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M163" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Исполнительный директор по финансам и обеспечению</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M164" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Советник по информационной безопасности</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M165" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Директор по финансовым  вопросам</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M166" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Главный финансовый менеджер</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M167" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Финансовый менеджер</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M168" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Главный бухгалтер</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M169" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Директор по правовым вопросам</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M170" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Заместитель директора по правовым вопросам</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M171" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Главный юрист</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M172" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Старший юрист</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M173" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Менеджер по безопасности</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M174" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Главный менеджер по ИБ</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M175" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Корпоративный секретарь</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M176" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Ассистент</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M177" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Заведующий складом</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M178" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Директор по управлению проектами</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M179" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Заместитель директора Департамента</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M180" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Аналитик по эффективности и рискам</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M181" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Младший менеджер проектов</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M182" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Начальник отдела по связям с общественностью и СМИ</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M183" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Мобильное рабочее место "Сергек"</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>ФЭМ №1 (Павлодар).xlsx::3. Инвест; ФЭМ №2 (Павлодар).xlsx::3. Инвест</t>
+        </is>
+      </c>
+      <c r="M184" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Распределение расходов административно-управленческого персонала,осуществляющего поддержку проекта Астана - Сергек ( прочие расходы)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>ФЭМ_Астана (4).xlsx::Обсл; ФЭМ_Астана (4).xlsx::Экспл</t>
+        </is>
+      </c>
+      <c r="M185" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Инвест</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Видеостена под ключ</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>ФЭМ_Атырау.xlsx::Инвест</t>
+        </is>
+      </c>
+      <c r="M186" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Аппаратно-программный комплекс "Сергек. Трасса" v4.0</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::3. Инвест; ФЭМ_проекта_Курмангазы v.8.xlsx::3. Инвест</t>
+        </is>
+      </c>
+      <c r="M187" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Главный инженер</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M188" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Старший бригадир</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M189" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Инженер ОКК</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M190" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Бригадир</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M191" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Старший монтажник</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M192" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Младший монтажник</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M193" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>4.CAPEX</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Видеостена (13500х6500), под ключ</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::4.CAPEX</t>
+        </is>
+      </c>
+      <c r="M194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Аппаратно-программный комплекс "Сергек. Патруль"</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>4. Шу_ФЭМ.xlsx::3. Инвест</t>
+        </is>
+      </c>
+      <c r="M195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Аппаратно-программный комплекс "Сергек. Трасса"</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>4. Шу_ФЭМ.xlsx::3. Инвест</t>
+        </is>
+      </c>
+      <c r="M196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Распределение расходов административно-управленческого персонала,осуществляющего поддержку проекта Астана - Сергек за  декабрь 2022г. ( прочие расходы)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::Обсл</t>
+        </is>
+      </c>
+      <c r="M197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>АПК "Сергек" на линейных участках</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>ФЭМ Костанай.xlsx::4.CAPEX</t>
+        </is>
+      </c>
+      <c r="M198" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>АПК "Сергек" на перекрестках</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>ФЭМ Костанай.xlsx::4.CAPEX</t>
+        </is>
+      </c>
+      <c r="M199" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Аппаратно-программный комплекс "Сергек. Трассы"</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>ФЭМ №2 (Павлодар).xlsx::3. Инвест</t>
+        </is>
+      </c>
+      <c r="M200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Аппаратно-программный комплекс "Сергек. Линейный участок" v4.0 на трассах</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Жетысу_final.xlsx::3. Инвест</t>
+        </is>
+      </c>
+      <c r="M201" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
         <is>
           <t>Аппаратно-программный комплекс "Сергек. Lite"</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>CAPEX</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t>ФЭМ_проекта_Курмангазы v.8.xlsx::3. Инвест</t>
         </is>
       </c>
-      <c r="M148" t="n">
+      <c r="M202" t="n">
         <v>1</v>
       </c>
     </row>
@@ -34645,7 +35995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M67"/>
+  <dimension ref="B2:M121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -36684,12 +38034,12 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Билеты (ж.д. сообщение, плацкарт, 2 направления)</t>
+          <t>Менеджер проектов</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -36699,22 +38049,22 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Билеты (ж.д. сообщение, купе, 2 направления)</t>
+          <t>Технический директор</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -36724,22 +38074,22 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Билеты (авиа сообщение,  2 направления)</t>
+          <t>Инженер контроля качества</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -36749,22 +38099,22 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Проживание (сутки гостиница для производств.сотрудников)</t>
+          <t>Бухгалтер</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -36774,22 +38124,22 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Проживание (сутки гостиница для АУП)</t>
+          <t>Директор филиала</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -36799,22 +38149,22 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>Экономические предположения</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Суточные (6 мрп)</t>
+          <t>Юрист</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -36824,7 +38174,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -36834,12 +38184,12 @@
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>7. Расчет экспл.расх</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ДТ для ДГУ</t>
+          <t>Инспектор по кадрам</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -36849,11 +38199,11 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
@@ -36864,7 +38214,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Охрана</t>
+          <t>Билеты (ж.д. сообщение, плацкарт, 2 направления)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -36878,7 +38228,7 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
@@ -36889,7 +38239,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Канц. Товары</t>
+          <t>Билеты (ж.д. сообщение, купе, 2 направления)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -36903,7 +38253,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
@@ -36914,7 +38264,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Хоз. Товары</t>
+          <t>Билеты (авиа сообщение,  2 направления)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -36928,7 +38278,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -36939,7 +38289,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Клининговые услуги</t>
+          <t>Проживание (сутки гостиница для производств.сотрудников)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -36953,7 +38303,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -36964,7 +38314,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ГСМ для сотрудников</t>
+          <t>Проживание (сутки гостиница для АУП)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -36974,22 +38324,22 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Туркестан фин 04.11.2025.xlsx::5. Экспл; ФЭМ №1 (Павлодар).xlsx::5. Экспл</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>7. Расчет экспл.расх</t>
+          <t>Экономические предположения</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Канал передачи данных - центральный узел</t>
+          <t>Суточные (6 мрп)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -36999,22 +38349,22 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх; ФЭМ №1 (Павлодар).xlsx::5. Экспл; ФЭМ_Туркестан_1006.xlsx::Экспл</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>Экспл</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Аренда ЦОД</t>
+          <t>Водитель логист</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -37024,22 +38374,22 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>ФЭМ ИТОГ до ноября24.xlsx::Экспл; ФЭМ_Астана (4).xlsx::Экспл</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ; ФЭМ_проекта_Жетысу_final.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>Экспл</t>
+          <t>Затраты по заработной плате</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Коммунальные расходы (электроэнергия)</t>
+          <t>Офис-менеджер</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -37049,22 +38399,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>ФЭМ ИТОГ до ноября24.xlsx::Экспл; ФЭМ_Астана (4).xlsx::Экспл</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ; ФЭМ_проекта_Жетысу_final.xlsx::6. ФОТ</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>5. Экспл</t>
+          <t>7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Обслуживание  АПК "Патруль"</t>
+          <t>ДТ для ДГУ</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -37074,22 +38424,22 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ФЭМ_проекта_Жетысу_final.xlsx::5. Экспл; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::5. Экспл; ФЭМ_проекта_Курмангазы v.8.xlsx::5. Экспл</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Экономические предположения</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Канал передачи данных - АПК "Сергек.Линейный"</t>
+          <t>Охрана</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -37099,22 +38449,22 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Экономические предположения</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Канал передачи данных - АПК "Сергек.Перекресток"</t>
+          <t>Канц. Товары</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -37124,22 +38474,22 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>Аппаратно-программные комплексы "Сергек"</t>
+          <t>Экономические предположения</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Распределение расходов административно-управленческого персонала,осуществляющего поддержку проекта Астана - Сергек ( прочие расходы)</t>
+          <t>Хоз. Товары</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -37149,35 +38499,1385 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>ФЭМ_Астана (4).xlsx::Обсл; ФЭМ_Астана (4).xlsx::Экспл</t>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Экономист</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Менеджер отдела закупа</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-04-21 Прил 3 ФЭМ_Акмола (35 млрд).xlsx::4.1.ФОТ; 2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Экономические предположения</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Клининговые услуги</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; 4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Экономические предположения</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ГСМ для сотрудников</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>4. Шу_ФЭМ.xlsx::5. Экспл; Прил_ФЭМ_Алм_обл_расширение_тарифы_для_3_ПК_19_03_2025_1.xlsx::5. Экспл; ФЭМ ДС №2 Алмобл 26.02 .xlsx::5. Экспл; ФЭМ Туркестан фин 04.11.2025.xlsx::5. Экспл; ФЭМ №1 (Павлодар).xlsx::5. Экспл</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Старший инженер контроля качества</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; 4. Шу_ФЭМ.xlsx::6. ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ; ФЭМ_проекта_Жетысу_final.xlsx::6. ФОТ; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>7. Расчет экспл.расх</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Канал передачи данных - центральный узел</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх; ФЭМ №1 (Павлодар).xlsx::5. Экспл; ФЭМ_Туркестан_1006.xlsx::Экспл</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ведущий инженер контроля качества</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Инженер сетей</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>ФЭМ Туркестан фин 04.11.2025.xlsx::6. ФОТ; финал_ФЭМ_проекта_Туркестан_расширение_и_продление_v_2_с_помесячн_графиком.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Экспл</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Аренда ЦОД</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::Экспл; ФЭМ_Астана (4).xlsx::Экспл</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Экспл</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Коммунальные расходы (электроэнергия)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::Экспл; ФЭМ_Астана (4).xlsx::Экспл</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ведущий менеджер проектов</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5. Экспл</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Обслуживание  АПК "Патруль"</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Жетысу_final.xlsx::5. Экспл; ФЭМ_проекта_Кульсары_Расширение_новый_состав_1_8.xlsx::5. Экспл; ФЭМ_проекта_Курмангазы v.8.xlsx::5. Экспл</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Старший специалист по тех. поддержке</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Специалист по тех. поддержке</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Менеджер по технике безопасности</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Калибровщик</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Логист тестировщик</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::5.Расчет ФОТ; ФЭМ Костанай.xlsx::5.Расчет ФОТ</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
           <t>Аппаратно-программные комплексы "Сергек"</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Канал передачи данных - АПК "Сергек.Линейный"</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Канал передачи данных - АПК "Сергек.Перекресток"</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2_ФЭМ_Костанай_3,5млрд_v3_в_коротком_виде2.xlsx::7. Расчет экспл.расх; ФЭМ Костанай.xlsx::7. Расчет экспл.расх</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Заместитель директора филиала</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Менеджер мониторинга</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ассистент руководителя</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Главный инженер контроля качества</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ведущий инженер по сервисам</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Инженер по сервисам</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Логист</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Генеральный директор</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Исполнительный директор по финансам и обеспечению</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Советник по информационной безопасности</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Директор по финансовым  вопросам</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Главный финансовый менеджер</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Финансовый менеджер</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Главный бухгалтер</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Директор по правовым вопросам</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Заместитель директора по правовым вопросам</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Главный юрист</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Старший юрист</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Менеджер по безопасности</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Главный менеджер по ИБ</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Корпоративный секретарь</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ассистент</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Заведующий складом</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Директор по управлению проектами</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Заместитель директора Департамента</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Аналитик по эффективности и рискам</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Младший менеджер проектов</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Начальник отдела по связям с общественностью и СМИ</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>ФЭМ ИТОГ до ноября24.xlsx::ФОТ н; ФЭМ_Астана (4).xlsx::ФОТ н</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Распределение расходов административно-управленческого персонала,осуществляющего поддержку проекта Астана - Сергек ( прочие расходы)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>ФЭМ_Астана (4).xlsx::Обсл; ФЭМ_Астана (4).xlsx::Экспл</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Главный инженер</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Старший бригадир</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Инженер ОКК</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Бригадир</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Старший монтажник</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Затраты по заработной плате</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Младший монтажник</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>ФЭМ_проекта_Курмангазы v.8.xlsx::6. ФОТ</t>
+        </is>
+      </c>
+      <c r="M120" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Аппаратно-программные комплексы "Сергек"</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
         <is>
           <t>Распределение расходов административно-управленческого персонала,осуществляющего поддержку проекта Астана - Сергек за  декабрь 2022г. ( прочие расходы)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>OPEX</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t>ФЭМ ИТОГ до ноября24.xlsx::Обсл</t>
         </is>
       </c>
-      <c r="M67" t="n">
+      <c r="M121" t="n">
         <v>1</v>
       </c>
     </row>
